--- a/docs/configs/Resources.xlsx
+++ b/docs/configs/Resources.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +27,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -43,8 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,11 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,199 +431,230 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>资源ID</t>
+          <t>编号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>出现频率</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>生命值</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>掉落数</t>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>掉落数量</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Freq</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Hp</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>wood</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>木材</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="D4" t="n">
         <v>0.35</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" t="n">
         <v>80</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>stone</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>岩石</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="D5" t="n">
         <v>0.3</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="E5" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>ore</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>矿石</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="D6" t="n">
         <v>0.1</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" t="n">
         <v>150</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>bush</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>灌木</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="D7" t="n">
         <v>0.15</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E7" t="n">
         <v>50</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>pebble</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>碎石</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="D8" t="n">
         <v>0.1</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E8" t="n">
         <v>60</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" t="n">
         <v>1</v>
       </c>
     </row>
